--- a/monitor_xlsx/20260304.xlsx
+++ b/monitor_xlsx/20260304.xlsx
@@ -544,10 +544,6 @@
           <t>+0.59%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.47%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.62%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+1.93%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-10.27%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -669,7 +649,6 @@
           <t>-966.15億</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>-399.46億</t>
@@ -707,7 +686,6 @@
           <t>67.64億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>46.14億</t>
@@ -718,8 +696,6 @@
           <t>230.69億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -737,15 +713,11 @@
           <t>133.33%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>145.37%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,11 +735,6 @@
           <t>-1298.54億</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -785,15 +752,11 @@
           <t>32058口</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>17022口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,7 +774,6 @@
           <t>71.39億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-2.77億</t>
@@ -916,10 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1041,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1076,6 +1034,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1267,7 +1226,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="G5" s="7" t="n">
         <v>-74</v>
       </c>
@@ -2110,6 +2068,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3467</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3485</v>
+      </c>
+      <c r="H19" t="n">
+        <v>455</v>
+      </c>
+      <c r="I19" t="n">
+        <v>862</v>
+      </c>
+      <c r="J19" t="n">
+        <v>271</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1979</v>
+      </c>
+      <c r="L19" t="n">
+        <v>11243</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-47572</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5102</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>-431</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-754</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-216</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-373</v>
+      </c>
+      <c r="J20" t="n">
+        <v>250</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1946</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9453</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-140182</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260304.xlsx
+++ b/monitor_xlsx/20260304.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2177,165 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>962</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>826</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>-97</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-27</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-55</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>624</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>873</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6793</v>
+      </c>
+      <c r="H22" t="n">
+        <v>188</v>
+      </c>
+      <c r="I22" t="n">
+        <v>211</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-28</v>
+      </c>
+      <c r="L22" t="n">
+        <v>31</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4739</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-1082</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3965</v>
+      </c>
+      <c r="H23" t="n">
+        <v>244</v>
+      </c>
+      <c r="I23" t="n">
+        <v>367</v>
+      </c>
+      <c r="J23" t="n">
+        <v>78</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2702</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10435</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106283</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260304.xlsx
+++ b/monitor_xlsx/20260304.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2336,6 +2336,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>237.5</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10896</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-421</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2976</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>405</v>
+      </c>
+      <c r="J24" t="n">
+        <v>246</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6962</v>
+      </c>
+      <c r="L24" t="n">
+        <v>34703</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-58841</v>
+      </c>
+      <c r="N24" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
